--- a/data-raw/rap_2026/Luku5.xlsx
+++ b/data-raw/rap_2026/Luku5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\03238715\Work Folders\R_pkg\fiprod\data-raw\rap_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A668D76D-C71B-4478-B878-1CF2C99FC026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC7DFC2-39F0-4585-9186-2B8A066AC705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="21180" windowHeight="11232" activeTab="5" xr2:uid="{FAAD0CD2-F287-4DDE-8F8C-7F9C76C9E0E6}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="21180" windowHeight="11232" activeTab="4" xr2:uid="{FAAD0CD2-F287-4DDE-8F8C-7F9C76C9E0E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Kuvio 16" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="168">
   <si>
     <t>Vuosi</t>
   </si>
@@ -543,6 +543,9 @@
   <si>
     <t>Yritysten taso</t>
   </si>
+  <si>
+    <t>Korkea teknologia</t>
+  </si>
 </sst>
 </file>
 
@@ -8173,7 +8176,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Korkean teknologia</c:v>
+                  <c:v>Korkea teknologia</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -17291,7 +17294,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.3">
@@ -18691,26 +18694,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40a5ec75-f348-4919-90d9-e715165c6509">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a2718a10-04c3-4bb2-bdc7-1a623746c748" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100550B5FBC35A3924EA7731349BDEFBC5F" ma:contentTypeVersion="13" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="a8aca18d713afea54fe8db5ad7623308">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40a5ec75-f348-4919-90d9-e715165c6509" xmlns:ns3="a2718a10-04c3-4bb2-bdc7-1a623746c748" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71bc00f1ce961b9364a36ba3652469d" ns2:_="" ns3:_="">
     <xsd:import namespace="40a5ec75-f348-4919-90d9-e715165c6509"/>
@@ -18933,32 +18916,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB69C90-33D2-4B49-AB46-2B5ACEA72568}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a2718a10-04c3-4bb2-bdc7-1a623746c748"/>
-    <ds:schemaRef ds:uri="40a5ec75-f348-4919-90d9-e715165c6509"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACDA5F7A-9302-42D1-984D-F84D1D7941A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40a5ec75-f348-4919-90d9-e715165c6509">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2718a10-04c3-4bb2-bdc7-1a623746c748" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73693894-0548-423E-BBDE-2DB9DF5CA66F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18975,4 +18953,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACDA5F7A-9302-42D1-984D-F84D1D7941A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB69C90-33D2-4B49-AB46-2B5ACEA72568}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a2718a10-04c3-4bb2-bdc7-1a623746c748"/>
+    <ds:schemaRef ds:uri="40a5ec75-f348-4919-90d9-e715165c6509"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data-raw/rap_2026/Luku5.xlsx
+++ b/data-raw/rap_2026/Luku5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\03238715\Work Folders\R_pkg\fiprod\data-raw\rap_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC7DFC2-39F0-4585-9186-2B8A066AC705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DF4D7C-850B-4E2F-8D56-7E468DC98E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="21180" windowHeight="11232" activeTab="4" xr2:uid="{FAAD0CD2-F287-4DDE-8F8C-7F9C76C9E0E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FAAD0CD2-F287-4DDE-8F8C-7F9C76C9E0E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Kuvio 16" sheetId="1" r:id="rId1"/>
@@ -529,12 +529,6 @@
     <t>Yhteensä</t>
   </si>
   <si>
-    <t>p&amp;k-yritykset</t>
-  </si>
-  <si>
-    <t>suuret yritykset</t>
-  </si>
-  <si>
     <t>year</t>
   </si>
   <si>
@@ -545,6 +539,12 @@
   </si>
   <si>
     <t>Korkea teknologia</t>
+  </si>
+  <si>
+    <t>P&amp;K-yritykset</t>
+  </si>
+  <si>
+    <t>Suuret yritykset</t>
   </si>
 </sst>
 </file>
@@ -16761,7 +16761,7 @@
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -16829,7 +16829,7 @@
     </row>
     <row r="8" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -16908,13 +16908,13 @@
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" t="s">
         <v>164</v>
-      </c>
-      <c r="C3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
@@ -17270,7 +17270,7 @@
   <sheetData>
     <row r="3" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
         <v>2</v>
@@ -17294,7 +17294,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.3">
@@ -18694,6 +18694,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40a5ec75-f348-4919-90d9-e715165c6509">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2718a10-04c3-4bb2-bdc7-1a623746c748" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100550B5FBC35A3924EA7731349BDEFBC5F" ma:contentTypeVersion="13" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="a8aca18d713afea54fe8db5ad7623308">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40a5ec75-f348-4919-90d9-e715165c6509" xmlns:ns3="a2718a10-04c3-4bb2-bdc7-1a623746c748" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71bc00f1ce961b9364a36ba3652469d" ns2:_="" ns3:_="">
     <xsd:import namespace="40a5ec75-f348-4919-90d9-e715165c6509"/>
@@ -18916,27 +18936,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB69C90-33D2-4B49-AB46-2B5ACEA72568}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a2718a10-04c3-4bb2-bdc7-1a623746c748"/>
+    <ds:schemaRef ds:uri="40a5ec75-f348-4919-90d9-e715165c6509"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40a5ec75-f348-4919-90d9-e715165c6509">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a2718a10-04c3-4bb2-bdc7-1a623746c748" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACDA5F7A-9302-42D1-984D-F84D1D7941A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73693894-0548-423E-BBDE-2DB9DF5CA66F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18953,29 +18978,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACDA5F7A-9302-42D1-984D-F84D1D7941A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB69C90-33D2-4B49-AB46-2B5ACEA72568}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a2718a10-04c3-4bb2-bdc7-1a623746c748"/>
-    <ds:schemaRef ds:uri="40a5ec75-f348-4919-90d9-e715165c6509"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>